--- a/exports/2026年3月报销付款统计报表.xlsx
+++ b/exports/2026年3月报销付款统计报表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="63">
   <si>
     <t>2026年3月报销统计报表</t>
   </si>
@@ -119,21 +119,6 @@
     <t>刘静</t>
   </si>
   <si>
-    <t>手机卡充值</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>快递费用</t>
-  </si>
-  <si>
-    <t>资料到付快递费</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
     <t>2月阿姨工资</t>
   </si>
   <si>
@@ -149,6 +134,12 @@
     <t>张雪亮</t>
   </si>
   <si>
+    <t>5号电池购买</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
     <t>员工福利</t>
   </si>
   <si>
@@ -158,6 +149,12 @@
     <t>2026-03-03</t>
   </si>
   <si>
+    <t>项目下午茶（虾、炸鸡）</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
     <t>A4打印纸购买</t>
   </si>
   <si>
@@ -204,15 +201,6 @@
   </si>
   <si>
     <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>2026年3月份宽带费</t>
-  </si>
-  <si>
-    <t>2026年3月餐费</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
   </si>
 </sst>
 </file>
@@ -945,55 +933,55 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="3">
-        <v>115</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="4">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3">
-        <v>27</v>
+        <v>550</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
@@ -1016,7 +1004,7 @@
         <v>30</v>
       </c>
       <c r="E14" s="4">
-        <v>207</v>
+        <v>550</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>17</v>
@@ -1033,7 +1021,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
@@ -1042,50 +1030,50 @@
         <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="3">
+        <v>41.2</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="3">
-        <v>550</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="E16" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="4">
-        <v>550</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="G16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1097,19 +1085,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="3">
-        <v>41.2</v>
+        <v>237.6</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
@@ -1126,19 +1114,19 @@
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3">
+        <v>170.4</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="3">
-        <v>237.6</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>16</v>
@@ -1158,16 +1146,16 @@
         <v>18</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3">
         <v>91.96</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>16</v>
@@ -1190,7 +1178,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="4">
-        <v>370.76</v>
+        <v>556.0600000000001</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>17</v>
@@ -1216,10 +1204,10 @@
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5">
-        <v>16880.719999999998</v>
+        <v>16924.019999999997</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>17</v>
@@ -1247,9 +1235,9 @@
     <hyperlink ref="H8" r:id="rId6"/>
     <hyperlink ref="H9" r:id="rId7"/>
     <hyperlink ref="H11" r:id="rId8"/>
-    <hyperlink ref="H12" r:id="rId9"/>
-    <hyperlink ref="H13" r:id="rId10"/>
-    <hyperlink ref="H15" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId9"/>
+    <hyperlink ref="H15" r:id="rId10"/>
+    <hyperlink ref="H16" r:id="rId11"/>
     <hyperlink ref="H17" r:id="rId12"/>
     <hyperlink ref="H18" r:id="rId13"/>
     <hyperlink ref="H19" r:id="rId14"/>
@@ -1261,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1274,7 +1262,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1290,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -1299,7 +1287,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1310,13 +1298,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3">
         <v>5979.82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
@@ -1330,13 +1318,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3">
         <v>25406</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -1350,13 +1338,13 @@
         <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3">
         <v>25000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>16</v>
@@ -1364,19 +1352,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D6" s="3">
         <v>1080</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>16</v>
@@ -1390,55 +1378,15 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3">
         <v>3330</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1080</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4680</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1452,8 +1400,6 @@
     <hyperlink ref="F5" r:id="rId3"/>
     <hyperlink ref="F6" r:id="rId4"/>
     <hyperlink ref="F7" r:id="rId5"/>
-    <hyperlink ref="F8" r:id="rId6"/>
-    <hyperlink ref="F9" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
